--- a/analysis/aggregate/ot-PRF.xlsx
+++ b/analysis/aggregate/ot-PRF.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -518,22 +518,22 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7802583286661582</v>
+        <v>0.7852898168394316</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03049035401308843</v>
+        <v>0.004078029139064131</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7752941176470588</v>
+        <v>0.7788235294117647</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02177265355684911</v>
+        <v>0.0114668168762458</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7776956395105732</v>
+        <v>0.7820141029886558</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02509835411834288</v>
+        <v>0.006780423274603079</v>
       </c>
     </row>
     <row r="3">
@@ -544,7 +544,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -571,22 +571,22 @@
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7802583286661582</v>
+        <v>0.7125098478502113</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03049035401308843</v>
+        <v>0.01303948032424609</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7752941176470588</v>
+        <v>0.7141176470588235</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02177265355684911</v>
+        <v>0.008921029934178336</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7776956395105732</v>
+        <v>0.7133039607730474</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02509835411834288</v>
+        <v>0.01081486411016003</v>
       </c>
     </row>
     <row r="4">
@@ -597,7 +597,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -624,22 +624,22 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7660862087319329</v>
+        <v>0.7597915734341074</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01222058371392725</v>
+        <v>0.01790981592976502</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7623529411764706</v>
+        <v>0.7552941176470588</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01146681687624585</v>
+        <v>0.01694689445986815</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7641539210158771</v>
+        <v>0.7575308718030858</v>
       </c>
       <c r="M4" t="n">
-        <v>0.008974274615300469</v>
+        <v>0.01728672654112732</v>
       </c>
     </row>
     <row r="5">
@@ -650,7 +650,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -677,22 +677,22 @@
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7660862087319329</v>
+        <v>0.696780265300828</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01222058371392725</v>
+        <v>0.02423935761051136</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7623529411764706</v>
+        <v>0.7023529411764706</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01146681687624585</v>
+        <v>0.01887859592456608</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7641539210158771</v>
+        <v>0.6995396075240035</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008974274615300469</v>
+        <v>0.02142215925435189</v>
       </c>
     </row>
     <row r="6">
@@ -703,7 +703,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -727,25 +727,25 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7983380316447887</v>
+        <v>0.8049630600518525</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01340382937547681</v>
+        <v>0.01241305607970119</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7828571428571428</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01360272081627208</v>
+        <v>0.01616244071283534</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7919338300058121</v>
+        <v>0.7937134647692754</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0117373654262594</v>
+        <v>0.0129248368070919</v>
       </c>
     </row>
     <row r="7">
@@ -756,7 +756,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -783,22 +783,22 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7988976980431037</v>
+        <v>0.8049630600518525</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01167532071645935</v>
+        <v>0.01241305607970119</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7897142857142857</v>
+        <v>0.7828571428571428</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01479106183490832</v>
+        <v>0.01616244071283534</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7942308246884103</v>
+        <v>0.7937134647692754</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0113888205368943</v>
+        <v>0.0129248368070919</v>
       </c>
     </row>
     <row r="8">
@@ -809,7 +809,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -836,22 +836,22 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8051872546058594</v>
+        <v>0.7657059210383406</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01424053997532936</v>
+        <v>0.02185188550398372</v>
       </c>
       <c r="J8" t="n">
-        <v>0.784</v>
+        <v>0.7748571428571429</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02036403392137769</v>
+        <v>0.01113919353692451</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7943833895959991</v>
+        <v>0.7701122825111085</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01563579646818549</v>
+        <v>0.01293941531815837</v>
       </c>
     </row>
     <row r="9">
@@ -862,48 +862,472 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>flan-t5-base</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7657059210383406</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02185188550398372</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7748571428571429</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01113919353692451</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.7701122825111085</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.01293941531815837</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>t5-base</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.7802583286661582</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.03049035401308843</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7752941176470588</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.02177265355684911</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7776956395105732</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.02509835411834288</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.7802583286661582</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.03049035401308843</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7752941176470588</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.02177265355684911</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.7776956395105732</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.02509835411834288</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7660862087319329</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.01222058371392725</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.7623529411764706</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.01146681687624585</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.7641539210158771</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.008974274615300469</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.7660862087319329</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.01222058371392725</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7623529411764706</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.01146681687624585</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.7641539210158771</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.008974274615300469</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>paraphrase</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.7983380316447887</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.01340382937547681</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.01360272081627208</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.7919338300058121</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0117373654262594</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.7988976980431037</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.01167532071645935</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.7897142857142857</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.01479106183490832</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.7942308246884103</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.0113888205368943</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="n">
         <v>0.8051872546058594</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I16" t="n">
         <v>0.01424053997532936</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J16" t="n">
         <v>0.784</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K16" t="n">
         <v>0.02036403392137769</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L16" t="n">
         <v>0.7943833895959991</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M16" t="n">
+        <v>0.01563579646818549</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8051872546058594</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.01424053997532936</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.02036403392137769</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.7943833895959991</v>
+      </c>
+      <c r="M17" t="n">
         <v>0.01563579646818549</v>
       </c>
     </row>

--- a/analysis/aggregate/ot-PRF.xlsx
+++ b/analysis/aggregate/ot-PRF.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -518,22 +518,22 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7852898168394316</v>
+        <v>0.7951110771428606</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004078029139064131</v>
+        <v>0.03368861646306708</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7788235294117647</v>
+        <v>0.7870588235294118</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0114668168762458</v>
+        <v>0.01832048412046762</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7820141029886558</v>
+        <v>0.7909785458584978</v>
       </c>
       <c r="M2" t="n">
-        <v>0.006780423274603079</v>
+        <v>0.02538225634799032</v>
       </c>
     </row>
     <row r="3">
@@ -554,39 +554,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7125098478502113</v>
+        <v>0.7774375637555274</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01303948032424609</v>
+        <v>0.02030376669288492</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7141176470588235</v>
+        <v>0.7717647058823529</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008921029934178336</v>
+        <v>0.01784205986835659</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7133039607730474</v>
+        <v>0.7745178402049381</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01081486411016003</v>
+        <v>0.01703499808340622</v>
       </c>
     </row>
     <row r="4">
@@ -612,7 +612,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -624,22 +624,22 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7597915734341074</v>
+        <v>0.765277166401899</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01790981592976502</v>
+        <v>0.02970449779121405</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7552941176470588</v>
+        <v>0.7576470588235293</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01694689445986815</v>
+        <v>0.01924167909858368</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7575308718030858</v>
+        <v>0.7613650177684674</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01728672654112732</v>
+        <v>0.02347391356596207</v>
       </c>
     </row>
     <row r="5">
@@ -670,29 +670,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.696780265300828</v>
+        <v>0.7574746946355242</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02423935761051136</v>
+        <v>0.02227250066887518</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7023529411764706</v>
+        <v>0.7564705882352941</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01887859592456608</v>
+        <v>0.01887859592456612</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6995396075240035</v>
+        <v>0.7569535093714922</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02142215925435189</v>
+        <v>0.02023612895816959</v>
       </c>
     </row>
     <row r="6">
@@ -730,22 +730,22 @@
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8049630600518525</v>
+        <v>0.799473614300491</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01241305607970119</v>
+        <v>0.01612851620937596</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7828571428571428</v>
+        <v>0.784</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01616244071283534</v>
+        <v>0.02536267545276813</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7937134647692754</v>
+        <v>0.7915891948499518</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0129248368070919</v>
+        <v>0.0196890678306725</v>
       </c>
     </row>
     <row r="7">
@@ -771,34 +771,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8049630600518525</v>
+        <v>0.7813877223893451</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01241305607970119</v>
+        <v>0.009866727373063528</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7828571428571428</v>
+        <v>0.76</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01616244071283534</v>
+        <v>0.01456862718169364</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7937134647692754</v>
+        <v>0.770536378303184</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0129248368070919</v>
+        <v>0.0121771838561496</v>
       </c>
     </row>
     <row r="8">
@@ -819,12 +819,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -836,22 +836,22 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7657059210383406</v>
+        <v>0.7964517198808736</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02185188550398372</v>
+        <v>0.01322058769422251</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7748571428571429</v>
+        <v>0.7782857142857142</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01113919353692451</v>
+        <v>0.01779704171702564</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7701122825111085</v>
+        <v>0.7872448989500371</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01293941531815837</v>
+        <v>0.01514688260967251</v>
       </c>
     </row>
     <row r="9">
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -882,29 +882,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7657059210383406</v>
+        <v>0.7790622490988588</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02185188550398372</v>
+        <v>0.01936047676976141</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7748571428571429</v>
+        <v>0.7645714285714286</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01113919353692451</v>
+        <v>0.01238827622210216</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7701122825111085</v>
+        <v>0.7716786754375915</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01293941531815837</v>
+        <v>0.01384262912943431</v>
       </c>
     </row>
     <row r="10">
@@ -925,7 +925,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -942,22 +942,22 @@
         <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7802583286661582</v>
+        <v>0.7666601574469983</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03049035401308843</v>
+        <v>0.04150770736438551</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7752941176470588</v>
+        <v>0.7588235294117647</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02177265355684911</v>
+        <v>0.01813062942049698</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7776956395105732</v>
+        <v>0.7623001326810226</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02509835411834288</v>
+        <v>0.02441632946968793</v>
       </c>
     </row>
     <row r="11">
@@ -978,39 +978,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7802583286661582</v>
+        <v>0.766888967561179</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03049035401308843</v>
+        <v>0.01435035607517864</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7752941176470588</v>
+        <v>0.7729411764705882</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02177265355684911</v>
+        <v>0.01354219345084863</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7776956395105732</v>
+        <v>0.7697770591989492</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02509835411834288</v>
+        <v>0.008600745973553274</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1048,22 +1048,22 @@
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7660862087319329</v>
+        <v>0.7696419738785358</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01222058371392725</v>
+        <v>0.02146584913026591</v>
       </c>
       <c r="J12" t="n">
         <v>0.7623529411764706</v>
       </c>
       <c r="K12" t="n">
-        <v>0.01146681687624585</v>
+        <v>0.02063020931382374</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7641539210158771</v>
+        <v>0.7659620257335884</v>
       </c>
       <c r="M12" t="n">
-        <v>0.008974274615300469</v>
+        <v>0.02061655427287017</v>
       </c>
     </row>
     <row r="13">
@@ -1094,29 +1094,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7660862087319329</v>
+        <v>0.7555196411479106</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01222058371392725</v>
+        <v>0.01563504998059653</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7623529411764706</v>
+        <v>0.76</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01146681687624585</v>
+        <v>0.01968611827138998</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7641539210158771</v>
+        <v>0.7577348331214647</v>
       </c>
       <c r="M13" t="n">
-        <v>0.008974274615300469</v>
+        <v>0.01723177213026775</v>
       </c>
     </row>
     <row r="14">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1151,25 +1151,25 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7983380316447887</v>
+        <v>0.8089945646789222</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01340382937547681</v>
+        <v>0.01468916672778971</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7988571428571428</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01360272081627208</v>
+        <v>0.01733228672926066</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7919338300058121</v>
+        <v>0.8038874893176</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0117373654262594</v>
+        <v>0.01589779852762345</v>
       </c>
     </row>
     <row r="15">
@@ -1190,39 +1190,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7988976980431037</v>
+        <v>0.7813743610594411</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01167532071645935</v>
+        <v>0.01245236422082172</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7897142857142857</v>
+        <v>0.776</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01479106183490832</v>
+        <v>0.0123882762221022</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7942308246884103</v>
+        <v>0.7786691725334107</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0113888205368943</v>
+        <v>0.01207918204904451</v>
       </c>
     </row>
     <row r="16">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1260,22 +1260,22 @@
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8051872546058594</v>
+        <v>0.813525984182815</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01424053997532936</v>
+        <v>0.0179399896764833</v>
       </c>
       <c r="J16" t="n">
-        <v>0.784</v>
+        <v>0.7874285714285715</v>
       </c>
       <c r="K16" t="n">
-        <v>0.02036403392137769</v>
+        <v>0.02661900502594769</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7943833895959991</v>
+        <v>0.8001264394654996</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01563579646818549</v>
+        <v>0.01979450273070145</v>
       </c>
     </row>
     <row r="17">
@@ -1306,29 +1306,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8051872546058594</v>
+        <v>0.7876668045618211</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01424053997532936</v>
+        <v>0.01751362230990964</v>
       </c>
       <c r="J17" t="n">
-        <v>0.784</v>
+        <v>0.7634285714285715</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02036403392137769</v>
+        <v>0.02698450046426881</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7943833895959991</v>
+        <v>0.775275228360146</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01563579646818549</v>
+        <v>0.02117470219847072</v>
       </c>
     </row>
   </sheetData>

--- a/analysis/aggregate/ot-PRF.xlsx
+++ b/analysis/aggregate/ot-PRF.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,32 +454,92 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>precision_mean</t>
+          <t>micro_precision_mean</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>precision_std</t>
+          <t>micro_precision_std</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>recall_mean</t>
+          <t>micro_recall_mean</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>recall_std</t>
+          <t>micro_recall_std</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>f1_mean</t>
+          <t>micro_f1_mean</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>f1_std</t>
+          <t>micro_f1_std</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>macro_precision_mean</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>macro_precision_std</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>macro_recall_mean</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>macro_recall_std</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>macro_f1_mean</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>macro_f1_std</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>weighted_precision_mean</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>weighted_precision_std</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>weighted_recall_mean</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>weighted_recall_std</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>weighted_f1_mean</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>weighted_f1_std</t>
         </is>
       </c>
     </row>
@@ -518,22 +578,58 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7951110771428606</v>
+        <v>0.8316408443594501</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03368861646306708</v>
+        <v>0.02076235639021007</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7870588235294118</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01832048412046762</v>
+        <v>0.01440876319284224</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7909785458584978</v>
+        <v>0.8274760148589679</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02538225634799032</v>
+        <v>0.01508134723206681</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.8454545454545455</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.01838726897627015</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.8440771349862259</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.01547366024240614</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.8370798898071625</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.01693105865611242</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.8445098039215688</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.01608859076449486</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.01440876319284224</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.8246666666666667</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.01436225991283807</v>
       </c>
     </row>
     <row r="3">
@@ -571,22 +667,58 @@
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7774375637555274</v>
+        <v>0.8176955778106028</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02030376669288492</v>
+        <v>0.0125954246055437</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7717647058823529</v>
+        <v>0.8117647058823529</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01784205986835659</v>
+        <v>0.01176470588235291</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7745178402049381</v>
+        <v>0.8146446163356108</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01703499808340622</v>
+        <v>0.00859885499951918</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.819283746556474</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.01073143315745595</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.8209366391184574</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.01168771539151313</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.8120110192837465</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.01052723741786896</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.8301960784313727</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.007793963495824252</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.8117647058823529</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.01176470588235291</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.8116078431372549</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.008819606971290021</v>
       </c>
     </row>
     <row r="4">
@@ -624,22 +756,58 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.765277166401899</v>
+        <v>0.8066535001219256</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02970449779121405</v>
+        <v>0.01434118980893063</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7576470588235293</v>
+        <v>0.7988235294117647</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01924167909858368</v>
+        <v>0.007669649888473721</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7613650177684674</v>
+        <v>0.8026363971489147</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02347391356596207</v>
+        <v>0.006975059864596059</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.8214876033057852</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.006504528348825056</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.8168044077134986</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.008148870224655175</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.8109641873278237</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.005623479615274081</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.8243137254901962</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.007885912765564732</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.7988235294117647</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.007669649888473721</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.8015294117647057</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.006773083757855544</v>
       </c>
     </row>
     <row r="5">
@@ -677,22 +845,58 @@
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7574746946355242</v>
+        <v>0.7997509568522829</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02227250066887518</v>
+        <v>0.01112959801189202</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7564705882352941</v>
+        <v>0.7988235294117647</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01887859592456612</v>
+        <v>0.0152260930653468</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7569535093714922</v>
+        <v>0.7992665276974126</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02023612895816959</v>
+        <v>0.01253349841673482</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.8088154269972453</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.01149952146817732</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.8079889807162534</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.01436738822083227</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.800495867768595</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.01289980018613122</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.8182352941176472</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.01150865144378758</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.7988235294117647</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.0152260930653468</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.7992156862745097</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.01317378590763982</v>
       </c>
     </row>
     <row r="6">
@@ -730,22 +934,58 @@
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.799473614300491</v>
+        <v>0.8158822651293119</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01612851620937596</v>
+        <v>0.0109028556871446</v>
       </c>
       <c r="J6" t="n">
-        <v>0.784</v>
+        <v>0.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02536267545276813</v>
+        <v>0.01851640199545103</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7915891948499518</v>
+        <v>0.8077892184470519</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0196890678306725</v>
+        <v>0.01265077471895383</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.824793388429752</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.01198426266344689</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.8165289256198347</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.01696509006909333</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.8129161747343566</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.01361368323522765</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.830857142857143</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.01167589528097286</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.01851640199545103</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.805839455782313</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.01376053910589254</v>
       </c>
     </row>
     <row r="7">
@@ -783,22 +1023,58 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7813877223893451</v>
+        <v>0.8037345949753112</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009866727373063528</v>
+        <v>0.007423742507739263</v>
       </c>
       <c r="J7" t="n">
-        <v>0.76</v>
+        <v>0.7817142857142857</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01456862718169364</v>
+        <v>0.01171080087538236</v>
       </c>
       <c r="L7" t="n">
-        <v>0.770536378303184</v>
+        <v>0.7925622073691316</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0121771838561496</v>
+        <v>0.009410713265410936</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.803030303030303</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.01193866103537168</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.7887052341597797</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.009622175865880439</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.7877764659582842</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.01079498485140318</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.823047619047619</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.01205900083480331</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.7817142857142857</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.01171080087538236</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.7918639455782313</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.01184153472148511</v>
       </c>
     </row>
     <row r="8">
@@ -836,22 +1112,58 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7964517198808736</v>
+        <v>0.8139555014030574</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01322058769422251</v>
+        <v>0.01190880275795282</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7782857142857142</v>
+        <v>0.7954285714285714</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01779704171702564</v>
+        <v>0.01912365774935026</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7872448989500371</v>
+        <v>0.8045661237399024</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01514688260967251</v>
+        <v>0.01545110018003889</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.8231129476584023</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.01507820984652531</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.8134986225895318</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01393160640054036</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.8109012199921292</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.01437635964753022</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.8279428571428571</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.01863549389345664</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.7954285714285714</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.01912365774935026</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.8022312925170068</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.01906041358430885</v>
       </c>
     </row>
     <row r="9">
@@ -889,22 +1201,58 @@
         <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7790622490988588</v>
+        <v>0.8058358891303726</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01936047676976141</v>
+        <v>0.01922696698842527</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7645714285714286</v>
+        <v>0.7908571428571428</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01238827622210216</v>
+        <v>0.01251937274297524</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7716786754375915</v>
+        <v>0.798203832221559</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01384262912943431</v>
+        <v>0.01365568613056738</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.8108815426997245</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.009298795953757624</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.8000000000000002</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.008568777418730467</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.7976151121605668</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.00811700117977888</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.8279047619047619</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.01261050924073478</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.7908571428571428</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.01251937274297524</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.7997006802721088</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.01180460099910292</v>
       </c>
     </row>
     <row r="10">
@@ -942,22 +1290,58 @@
         <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7666601574469983</v>
+        <v>0.8138278276579509</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04150770736438551</v>
+        <v>0.03232866130486816</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7588235294117647</v>
+        <v>0.8058823529411765</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01813062942049698</v>
+        <v>0.01556324300626228</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7623001326810226</v>
+        <v>0.8093905799267824</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02441632946968793</v>
+        <v>0.01328561651829659</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.8198347107438018</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.02757230351300533</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.8168044077134986</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.008656890557835126</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.8103581267217631</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.01593110827831089</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.8284313725490197</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.02196603578667465</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.8058823529411765</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.01556324300626228</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.8074901960784313</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.01009604016001944</v>
       </c>
     </row>
     <row r="11">
@@ -995,22 +1379,58 @@
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.766888967561179</v>
+        <v>0.8088541259563261</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01435035607517864</v>
+        <v>0.01462418264749909</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7729411764705882</v>
+        <v>0.8152941176470587</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01354219345084863</v>
+        <v>0.01744987879316628</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7697770591989492</v>
+        <v>0.8119292256346686</v>
       </c>
       <c r="M11" t="n">
-        <v>0.008600745973553274</v>
+        <v>0.01130648434241074</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.8150137741046833</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0135274050819029</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.8190082644628098</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0176555869908147</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.8096182605273515</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.01457444858946136</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.8271568627450983</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.008501758191638741</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.8152941176470587</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.01744987879316628</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.8128123249299719</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.01187624860203934</v>
       </c>
     </row>
     <row r="12">
@@ -1048,22 +1468,58 @@
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7696419738785358</v>
+        <v>0.8135659891871091</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02146584913026591</v>
+        <v>0.01250319258351624</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7623529411764706</v>
+        <v>0.8058823529411765</v>
       </c>
       <c r="K12" t="n">
-        <v>0.02063020931382374</v>
+        <v>0.01315334104411642</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7659620257335884</v>
+        <v>0.8096869565294146</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02061655427287017</v>
+        <v>0.01205628308343585</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.8190082644628101</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.01138344546082332</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.8159779614325069</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.01517028639367314</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.8106887052341598</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.01380354979458824</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.8247058823529413</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.009439297962283004</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.8058823529411765</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.01315334104411642</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.8065490196078431</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.01280798962489623</v>
       </c>
     </row>
     <row r="13">
@@ -1101,22 +1557,58 @@
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7555196411479106</v>
+        <v>0.791828134454704</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01563504998059653</v>
+        <v>0.01658454205876776</v>
       </c>
       <c r="J13" t="n">
-        <v>0.76</v>
+        <v>0.7964705882352942</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01968611827138998</v>
+        <v>0.01793876550820813</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7577348331214647</v>
+        <v>0.7941233844971582</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01723177213026775</v>
+        <v>0.01667916385708706</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.7936639118457303</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.01718730110998795</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.7988980716253444</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.02107032856856519</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.7890358126721764</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.01938814714405078</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.8050980392156865</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.01262005020002435</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.7964705882352942</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.01793876550820813</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.792313725490196</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.01577572534587198</v>
       </c>
     </row>
     <row r="14">
@@ -1154,22 +1646,58 @@
         <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8089945646789222</v>
+        <v>0.8229015499348996</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01468916672778971</v>
+        <v>0.01469473667354226</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7988571428571428</v>
+        <v>0.8125714285714286</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01733228672926066</v>
+        <v>0.01636322407231582</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8038874893176</v>
+        <v>0.8176972886265018</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01589779852762345</v>
+        <v>0.0153534304840046</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.8278236914600552</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.01787982780405941</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.8245179063360883</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.02035121053635349</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.818473042109406</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.01961873617128149</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.8354285714285714</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.01171080087538239</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.8125714285714286</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.01636322407231582</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.8150421768707481</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.01527213641801666</v>
       </c>
     </row>
     <row r="15">
@@ -1207,22 +1735,58 @@
         <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7813743610594411</v>
+        <v>0.7963440016016419</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01245236422082172</v>
+        <v>0.01127070533949391</v>
       </c>
       <c r="J15" t="n">
-        <v>0.776</v>
+        <v>0.7908571428571428</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0123882762221022</v>
+        <v>0.01038051549976281</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7786691725334107</v>
+        <v>0.7935821921566664</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01207918204904451</v>
+        <v>0.01042313377538424</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.7935261707988981</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.01010309687101502</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.7933884297520661</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.00988477967934394</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.78616292798111</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.00999244605369372</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.809047619047619</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.01014632178698216</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.7908571428571428</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.01038051549976281</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.7919455782312925</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.01019714957281844</v>
       </c>
     </row>
     <row r="16">
@@ -1260,22 +1824,58 @@
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.813525984182815</v>
+        <v>0.8278086097135768</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0179399896764833</v>
+        <v>0.01600613367542084</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7874285714285715</v>
+        <v>0.801142857142857</v>
       </c>
       <c r="K16" t="n">
-        <v>0.02661900502594769</v>
+        <v>0.0211505777409391</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8001264394654996</v>
+        <v>0.8141164385081341</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01979450273070145</v>
+        <v>0.01472643393877005</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.8250688705234162</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.02040706940775344</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.8151515151515152</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.02004120397946756</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.8126249508067691</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.01883638865583575</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.8337142857142859</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.01557077324964424</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.801142857142857</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.0211505777409391</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.8079020408163264</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.01666161356134733</v>
       </c>
     </row>
     <row r="17">
@@ -1313,22 +1913,58 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7876668045618211</v>
+        <v>0.8113753185369234</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01751362230990964</v>
+        <v>0.01607890189004627</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7634285714285715</v>
+        <v>0.7862857142857143</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02698450046426881</v>
+        <v>0.02160876617278744</v>
       </c>
       <c r="L17" t="n">
-        <v>0.775275228360146</v>
+        <v>0.7985473646133381</v>
       </c>
       <c r="M17" t="n">
-        <v>0.02117470219847072</v>
+        <v>0.01677629975951919</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.7982093663911846</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.02141640744554579</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.787878787878788</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.02844611078245646</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.7860369933097207</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.02483837737811729</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.8187619047619048</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.01088800959011646</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.7862857142857143</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.02160876617278744</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.7941986394557823</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.0163183925295787</v>
       </c>
     </row>
   </sheetData>
